--- a/research themes.xlsx
+++ b/research themes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomso\Desktop\LM2-website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC9BA455-5CF9-4A00-8A8B-0B24B5E47436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB58FF1E-3936-461A-A302-568B9F9D2788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="13920" xr2:uid="{A228F791-D77F-4976-A0F0-616635C7D355}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A228F791-D77F-4976-A0F0-616635C7D355}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,46 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>additive manufacturing</t>
-  </si>
-  <si>
-    <t>multiscale mechanics</t>
-  </si>
-  <si>
-    <t>multistable structures</t>
-  </si>
-  <si>
-    <t>biomimetics and bio-inspired systems</t>
-  </si>
-  <si>
-    <t>monitoring and digital twins</t>
-  </si>
-  <si>
-    <t>additive manufacturing of smart composites</t>
-  </si>
-  <si>
-    <t>fluids, and slender structures</t>
-  </si>
-  <si>
-    <t>fabrication additive</t>
-  </si>
-  <si>
-    <t>mécanique multi-échelle</t>
-  </si>
-  <si>
-    <t>structures multistables</t>
-  </si>
-  <si>
-    <t>biomimétique et les systèmes bio-inspirés</t>
-  </si>
-  <si>
-    <t>fabrication additive de composites intelligents</t>
-  </si>
-  <si>
-    <t>fluides et les structures élancées</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
   <si>
     <t>Métamatériaux mécaniques</t>
   </si>
@@ -89,10 +50,64 @@
     <t>Robotique souple</t>
   </si>
   <si>
-    <t>interactions fluide-structure</t>
-  </si>
-  <si>
-    <t>jumeaux numériques ou physics-informed machine learning</t>
+    <t>Additive Manufacturing</t>
+  </si>
+  <si>
+    <t>Multiscale Mechanics</t>
+  </si>
+  <si>
+    <t>Multistable Structures</t>
+  </si>
+  <si>
+    <t>Biomimetics and Bio-Inspired Systems</t>
+  </si>
+  <si>
+    <t>Additive Manufacturing of Smart Composites</t>
+  </si>
+  <si>
+    <t>Fluids and Slender Structures</t>
+  </si>
+  <si>
+    <t>Mechanical Metamaterials</t>
+  </si>
+  <si>
+    <t>Deployable Structures Inspired by Origami and Kirigami</t>
+  </si>
+  <si>
+    <t>Soft Robotics</t>
+  </si>
+  <si>
+    <t>Fluid–Structure Interactions (FSI)</t>
+  </si>
+  <si>
+    <t>Fabrication additive de composites intelligents</t>
+  </si>
+  <si>
+    <t>Biomimétique et les systèmes bio-inspirés</t>
+  </si>
+  <si>
+    <t>Structures multistables</t>
+  </si>
+  <si>
+    <t>Mécanique multi-échelle</t>
+  </si>
+  <si>
+    <t>Fabrication additive</t>
+  </si>
+  <si>
+    <t>Interactions fluide-structure</t>
+  </si>
+  <si>
+    <t>Digital Twins &amp; Physics-Informed AI</t>
+  </si>
+  <si>
+    <t>Biomimetics &amp; Bio-Inspired Systems</t>
+  </si>
+  <si>
+    <t>Fluid–Structure Interactions</t>
+  </si>
+  <si>
+    <t>Jumeaux numériques et IA guidée par la physique</t>
   </si>
 </sst>
 </file>
@@ -108,12 +123,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -128,8 +149,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,83 +487,146 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAB81D6D-55AF-4E72-B326-D8D871BF9790}">
-  <dimension ref="B4:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B4:D25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
         <v>0</v>
       </c>
-      <c r="G4" t="s">
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G11" t="s">
+      <c r="D24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G14" t="s">
-        <v>16</v>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
